--- a/data/trans_orig/P6709-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6709-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2012</t>
+          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2012 (tasa de respuesta: 98,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30315</t>
+          <t>30690</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21584</t>
+          <t>21827</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>23011</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47420</t>
+          <t>45470</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28877</t>
+          <t>30155</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18771</t>
+          <t>19726</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19338</t>
+          <t>20119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41861</t>
+          <t>42620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36040</t>
+          <t>36025</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60582</t>
+          <t>62464</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>21755</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43730</t>
+          <t>42499</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62932</t>
+          <t>63709</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94904</t>
+          <t>95414</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52572</t>
+          <t>52522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81185</t>
+          <t>83363</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30856</t>
+          <t>30762</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53733</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90596</t>
+          <t>89590</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125539</t>
+          <t>127800</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100502</t>
+          <t>99384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>131802</t>
+          <t>132161</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52382</t>
+          <t>51883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77202</t>
+          <t>76377</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>159664</t>
+          <t>156647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200723</t>
+          <t>198500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15668</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40076</t>
+          <t>37660</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14182</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32936</t>
+          <t>34048</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33358</t>
+          <t>34514</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63625</t>
+          <t>65106</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39558</t>
+          <t>40853</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34883</t>
+          <t>35298</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>39308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68247</t>
+          <t>66561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66135</t>
+          <t>64823</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99416</t>
+          <t>97872</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38961</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65800</t>
+          <t>66365</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>113107</t>
+          <t>114029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>155340</t>
+          <t>154555</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89552</t>
+          <t>90493</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128691</t>
+          <t>130106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44362</t>
+          <t>43262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71414</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139994</t>
+          <t>144610</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>187556</t>
+          <t>190513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145344</t>
+          <t>146623</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>187546</t>
+          <t>188443</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98017</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131096</t>
+          <t>133340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>256168</t>
+          <t>255130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310727</t>
+          <t>306663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>13861</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35289</t>
+          <t>34471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>13561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31099</t>
+          <t>30883</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31922</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57924</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36590</t>
+          <t>37444</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>15068</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46770</t>
+          <t>44463</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45930</t>
+          <t>44802</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75011</t>
+          <t>75002</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32350</t>
+          <t>31583</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59680</t>
+          <t>56619</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>84930</t>
+          <t>84698</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>125661</t>
+          <t>122515</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54089</t>
+          <t>54393</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86814</t>
+          <t>85452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35117</t>
+          <t>35729</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58659</t>
+          <t>60847</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>97059</t>
+          <t>95048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137212</t>
+          <t>133906</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>128446</t>
+          <t>128887</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>166021</t>
+          <t>166600</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78580</t>
+          <t>78128</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>109003</t>
+          <t>109080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>215217</t>
+          <t>215120</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>265110</t>
+          <t>263609</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>21144</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44142</t>
+          <t>43992</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22776</t>
+          <t>23747</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>46691</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48665</t>
+          <t>49186</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81157</t>
+          <t>80754</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40834</t>
+          <t>41521</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38184</t>
+          <t>39339</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40551</t>
+          <t>40446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>69766</t>
+          <t>73328</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>90903</t>
+          <t>92183</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>127287</t>
+          <t>126882</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56225</t>
+          <t>55352</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85445</t>
+          <t>84343</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>156475</t>
+          <t>156017</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>202555</t>
+          <t>200555</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>96097</t>
+          <t>95621</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132913</t>
+          <t>131524</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52294</t>
+          <t>52544</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>79941</t>
+          <t>81507</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>158200</t>
+          <t>157381</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>204743</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117171</t>
+          <t>115956</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>156673</t>
+          <t>154577</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>84883</t>
+          <t>85752</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>118323</t>
+          <t>118630</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>214880</t>
+          <t>214899</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>264341</t>
+          <t>267524</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,45%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>79594</t>
+          <t>78148</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>120522</t>
+          <t>118399</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>75015</t>
+          <t>71686</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>110431</t>
+          <t>110813</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>160064</t>
+          <t>163329</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>217943</t>
+          <t>219252</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>80968</t>
+          <t>81554</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>121206</t>
+          <t>119531</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>52296</t>
+          <t>51743</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>88417</t>
+          <t>88337</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>142534</t>
+          <t>141974</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>194745</t>
+          <t>195651</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>265252</t>
+          <t>264048</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>328253</t>
+          <t>329847</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>167984</t>
+          <t>169162</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>223492</t>
+          <t>223138</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>452047</t>
+          <t>449692</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>536118</t>
+          <t>533137</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>324434</t>
+          <t>323291</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>393412</t>
+          <t>393347</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>184042</t>
+          <t>186191</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>241139</t>
+          <t>237077</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>523479</t>
+          <t>525727</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>610284</t>
+          <t>606867</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>526027</t>
+          <t>526995</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>603274</t>
+          <t>603724</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>341515</t>
+          <t>343983</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>405039</t>
+          <t>405738</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>890026</t>
+          <t>893456</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>988726</t>
+          <t>989120</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2016</t>
+          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17049</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36991</t>
+          <t>36243</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15679</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33535</t>
+          <t>32598</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>36997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64373</t>
+          <t>61917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24639</t>
+          <t>24895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46328</t>
+          <t>46264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30407</t>
+          <t>30773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41308</t>
+          <t>40157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70038</t>
+          <t>67617</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48461</t>
+          <t>47551</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75949</t>
+          <t>74820</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24814</t>
+          <t>23534</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44724</t>
+          <t>43336</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78804</t>
+          <t>79451</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>111276</t>
+          <t>110819</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37724</t>
+          <t>39224</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63938</t>
+          <t>65355</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40618</t>
+          <t>40675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63483</t>
+          <t>65102</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86386</t>
+          <t>86326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121308</t>
+          <t>121526</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58498</t>
+          <t>59014</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87896</t>
+          <t>89689</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28914</t>
+          <t>28436</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50454</t>
+          <t>49695</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92940</t>
+          <t>93707</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>129355</t>
+          <t>128944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31857</t>
+          <t>32376</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57583</t>
+          <t>58172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20764</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>41648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58472</t>
+          <t>57980</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92520</t>
+          <t>93103</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44703</t>
+          <t>44401</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73531</t>
+          <t>74421</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,82 +5183,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>17,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>44849</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>33221</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>57462</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>16,38%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>12,13%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>20,99%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>102226</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>84310</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>122180</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>14,86%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>17,76%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>44849</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>33342</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>58096</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>16,38%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>12,18%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>21,22%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>102226</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>84504</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>121769</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77293</t>
+          <t>78987</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>115192</t>
+          <t>113728</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51430</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78230</t>
+          <t>79940</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>137843</t>
+          <t>136445</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>183076</t>
+          <t>183126</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81266</t>
+          <t>80320</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117845</t>
+          <t>116154</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42485</t>
+          <t>42659</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67652</t>
+          <t>68680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131130</t>
+          <t>131413</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177736</t>
+          <t>176469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102505</t>
+          <t>100840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140120</t>
+          <t>140012</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65875</t>
+          <t>63914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96360</t>
+          <t>95151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>176726</t>
+          <t>173943</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224396</t>
+          <t>224125</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,59%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29649</t>
+          <t>29835</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55046</t>
+          <t>57404</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16045</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35335</t>
+          <t>35149</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51320</t>
+          <t>50018</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82221</t>
+          <t>82395</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40432</t>
+          <t>41032</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67589</t>
+          <t>68232</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38000</t>
+          <t>38873</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63666</t>
+          <t>64731</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>87457</t>
+          <t>86364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123762</t>
+          <t>123836</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96343</t>
+          <t>98078</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134824</t>
+          <t>133782</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>77245</t>
+          <t>76719</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>108152</t>
+          <t>107750</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>181573</t>
+          <t>179564</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>231380</t>
+          <t>230689</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60778</t>
+          <t>59080</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93250</t>
+          <t>92901</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32117</t>
+          <t>32735</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56394</t>
+          <t>56855</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99204</t>
+          <t>99288</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138845</t>
+          <t>137903</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63783</t>
+          <t>62791</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96408</t>
+          <t>96450</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47391</t>
+          <t>48177</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75029</t>
+          <t>74354</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>119647</t>
+          <t>119827</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>163827</t>
+          <t>163043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32531</t>
+          <t>32518</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57858</t>
+          <t>57813</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21668</t>
+          <t>23045</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43787</t>
+          <t>45815</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60500</t>
+          <t>59846</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93967</t>
+          <t>92728</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31012</t>
+          <t>32185</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56435</t>
+          <t>56552</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>24933</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48233</t>
+          <t>47616</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>61845</t>
+          <t>61388</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>96851</t>
+          <t>94029</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>88760</t>
+          <t>88206</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>122452</t>
+          <t>123434</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61276</t>
+          <t>60230</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91000</t>
+          <t>90638</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>157256</t>
+          <t>158860</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>204817</t>
+          <t>202981</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80387</t>
+          <t>81879</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>115340</t>
+          <t>115110</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71667</t>
+          <t>71939</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105288</t>
+          <t>102834</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>161571</t>
+          <t>160064</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>206690</t>
+          <t>210880</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>95882</t>
+          <t>94549</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>132678</t>
+          <t>130528</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>81713</t>
+          <t>81344</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>116029</t>
+          <t>114155</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>184506</t>
+          <t>182973</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>232966</t>
+          <t>233621</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>130281</t>
+          <t>130460</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>181842</t>
+          <t>177202</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>90577</t>
+          <t>93070</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>129420</t>
+          <t>131500</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>235043</t>
+          <t>233025</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>294609</t>
+          <t>299007</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>162647</t>
+          <t>162868</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>214470</t>
+          <t>216988</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>126839</t>
+          <t>129095</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>170905</t>
+          <t>176792</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>301717</t>
+          <t>303796</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>373570</t>
+          <t>373233</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>343032</t>
+          <t>342700</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>412705</t>
+          <t>411205</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>238166</t>
+          <t>238857</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>290770</t>
+          <t>294122</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>602069</t>
+          <t>596678</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>691261</t>
+          <t>686570</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>285910</t>
+          <t>290987</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>352403</t>
+          <t>353453</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>209617</t>
+          <t>210796</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>261602</t>
+          <t>266907</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>515673</t>
+          <t>518572</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>597537</t>
+          <t>603207</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>350384</t>
+          <t>348712</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>419491</t>
+          <t>421042</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>250980</t>
+          <t>247956</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>306705</t>
+          <t>304775</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>615537</t>
+          <t>613060</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>705161</t>
+          <t>704282</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6709-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6709-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>30089</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21827</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23011</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45470</t>
+          <t>45641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>11617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30155</t>
+          <t>30083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>19398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42620</t>
+          <t>41924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36025</t>
+          <t>36315</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62464</t>
+          <t>61987</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21755</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42499</t>
+          <t>43303</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63709</t>
+          <t>63974</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>95414</t>
+          <t>96409</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52522</t>
+          <t>52913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83363</t>
+          <t>81881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>30140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53623</t>
+          <t>53053</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89590</t>
+          <t>89812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127800</t>
+          <t>125854</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99384</t>
+          <t>98776</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>132161</t>
+          <t>131224</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51883</t>
+          <t>51226</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76377</t>
+          <t>76936</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>156647</t>
+          <t>158044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>198500</t>
+          <t>201032</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,95%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37660</t>
+          <t>37652</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>14219</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34048</t>
+          <t>33383</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34514</t>
+          <t>34584</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65106</t>
+          <t>63532</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18157</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40853</t>
+          <t>39766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15471</t>
+          <t>15178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35298</t>
+          <t>34060</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39308</t>
+          <t>38131</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66561</t>
+          <t>66590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64823</t>
+          <t>67669</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97872</t>
+          <t>100178</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39169</t>
+          <t>39074</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66365</t>
+          <t>66624</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>114029</t>
+          <t>111215</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>154555</t>
+          <t>154557</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90493</t>
+          <t>91109</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130106</t>
+          <t>127869</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43262</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70555</t>
+          <t>70141</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>144610</t>
+          <t>141917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190513</t>
+          <t>190057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146623</t>
+          <t>146611</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188443</t>
+          <t>186172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>97309</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133340</t>
+          <t>131467</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>255130</t>
+          <t>253936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>306663</t>
+          <t>310600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,82%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34471</t>
+          <t>35226</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>14221</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30883</t>
+          <t>31926</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32016</t>
+          <t>32461</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59243</t>
+          <t>59330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37444</t>
+          <t>38080</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>14948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>21773</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44463</t>
+          <t>45180</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44802</t>
+          <t>45551</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75002</t>
+          <t>73603</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31583</t>
+          <t>32070</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56619</t>
+          <t>58347</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>84698</t>
+          <t>82848</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>122515</t>
+          <t>121716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54393</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85452</t>
+          <t>84824</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35729</t>
+          <t>35624</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60847</t>
+          <t>60839</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95048</t>
+          <t>95559</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133906</t>
+          <t>133381</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>128887</t>
+          <t>126705</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>166600</t>
+          <t>164319</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78128</t>
+          <t>78632</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>109080</t>
+          <t>109576</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>215120</t>
+          <t>215517</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>263609</t>
+          <t>265434</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21144</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43992</t>
+          <t>43014</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23747</t>
+          <t>24724</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46691</t>
+          <t>47879</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49186</t>
+          <t>48807</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80754</t>
+          <t>82090</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>18074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41521</t>
+          <t>39342</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17361</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39339</t>
+          <t>37983</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40446</t>
+          <t>41687</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>73328</t>
+          <t>73726</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92183</t>
+          <t>93059</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>126882</t>
+          <t>129539</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55352</t>
+          <t>56594</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84343</t>
+          <t>88605</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>156017</t>
+          <t>154257</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>200555</t>
+          <t>203805</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95621</t>
+          <t>97291</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>131524</t>
+          <t>132906</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52544</t>
+          <t>52978</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81507</t>
+          <t>81886</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>157381</t>
+          <t>157026</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>203379</t>
+          <t>206178</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>115956</t>
+          <t>116381</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154577</t>
+          <t>156332</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>85752</t>
+          <t>85247</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>118630</t>
+          <t>117629</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>214899</t>
+          <t>213622</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>267524</t>
+          <t>267158</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>78148</t>
+          <t>78124</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>118399</t>
+          <t>120454</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>71686</t>
+          <t>72877</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>110813</t>
+          <t>110186</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>163329</t>
+          <t>160822</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>219252</t>
+          <t>217210</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>81554</t>
+          <t>79240</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>119531</t>
+          <t>120294</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51743</t>
+          <t>53263</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>88337</t>
+          <t>86770</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>141974</t>
+          <t>146056</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>195651</t>
+          <t>197377</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>264048</t>
+          <t>266200</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>329847</t>
+          <t>329156</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>169162</t>
+          <t>170709</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>223138</t>
+          <t>224412</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>449692</t>
+          <t>450901</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>533137</t>
+          <t>535863</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>323291</t>
+          <t>323562</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>393347</t>
+          <t>389976</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>186191</t>
+          <t>186581</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>237077</t>
+          <t>236972</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>525727</t>
+          <t>524110</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>606867</t>
+          <t>609941</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>526995</t>
+          <t>527795</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>603724</t>
+          <t>605674</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>343983</t>
+          <t>340818</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>405738</t>
+          <t>404481</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>893456</t>
+          <t>889055</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>989120</t>
+          <t>987087</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16693</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36243</t>
+          <t>36081</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32598</t>
+          <t>33539</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36997</t>
+          <t>37327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61917</t>
+          <t>64094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24895</t>
+          <t>24311</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46264</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30773</t>
+          <t>30354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40157</t>
+          <t>40456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67617</t>
+          <t>67454</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47551</t>
+          <t>46958</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74820</t>
+          <t>74854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23534</t>
+          <t>24073</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43336</t>
+          <t>43372</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>79451</t>
+          <t>77065</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>110819</t>
+          <t>110468</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39224</t>
+          <t>40328</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65355</t>
+          <t>65359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40675</t>
+          <t>40606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65102</t>
+          <t>63952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86326</t>
+          <t>85985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121526</t>
+          <t>120462</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59014</t>
+          <t>57536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89689</t>
+          <t>86568</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28436</t>
+          <t>28982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49695</t>
+          <t>50607</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93707</t>
+          <t>94146</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>128944</t>
+          <t>131163</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32376</t>
+          <t>31928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58172</t>
+          <t>59451</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>20845</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41648</t>
+          <t>41230</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57980</t>
+          <t>58340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93103</t>
+          <t>91211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44401</t>
+          <t>44405</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74421</t>
+          <t>74645</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33221</t>
+          <t>34388</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57462</t>
+          <t>59024</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84310</t>
+          <t>84380</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>122180</t>
+          <t>122091</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78987</t>
+          <t>76519</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>113728</t>
+          <t>114613</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>51452</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79940</t>
+          <t>77692</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>136445</t>
+          <t>137765</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>183126</t>
+          <t>183449</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80320</t>
+          <t>80507</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116154</t>
+          <t>117415</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42659</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68680</t>
+          <t>70986</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131413</t>
+          <t>130842</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176469</t>
+          <t>173096</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100840</t>
+          <t>101678</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140012</t>
+          <t>139617</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63914</t>
+          <t>65588</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95151</t>
+          <t>96865</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173943</t>
+          <t>176270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224125</t>
+          <t>226186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29835</t>
+          <t>30050</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57404</t>
+          <t>55893</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>15539</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35149</t>
+          <t>36254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50018</t>
+          <t>51956</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82395</t>
+          <t>83140</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41032</t>
+          <t>40185</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68232</t>
+          <t>68877</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38873</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64731</t>
+          <t>64047</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86364</t>
+          <t>86032</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123836</t>
+          <t>122932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98078</t>
+          <t>96466</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133782</t>
+          <t>133592</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76719</t>
+          <t>78561</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>107750</t>
+          <t>109277</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>179564</t>
+          <t>183713</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>230689</t>
+          <t>231237</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59080</t>
+          <t>59770</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92901</t>
+          <t>90427</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32735</t>
+          <t>32131</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56855</t>
+          <t>55116</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99288</t>
+          <t>98604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137903</t>
+          <t>139304</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62791</t>
+          <t>62021</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96450</t>
+          <t>94199</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48177</t>
+          <t>46069</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>74354</t>
+          <t>74765</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>119827</t>
+          <t>119307</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>163043</t>
+          <t>161264</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32518</t>
+          <t>31991</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57813</t>
+          <t>56390</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>22846</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45815</t>
+          <t>45827</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59846</t>
+          <t>59338</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92728</t>
+          <t>93406</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32185</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56552</t>
+          <t>58009</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24933</t>
+          <t>25668</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47616</t>
+          <t>47363</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>61388</t>
+          <t>61599</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94029</t>
+          <t>95908</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>88206</t>
+          <t>87504</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>123434</t>
+          <t>122489</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60230</t>
+          <t>60291</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>90638</t>
+          <t>91618</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>158860</t>
+          <t>158677</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>202981</t>
+          <t>206012</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>81879</t>
+          <t>81956</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>115110</t>
+          <t>117005</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71939</t>
+          <t>70074</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102834</t>
+          <t>102919</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160064</t>
+          <t>161507</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>210880</t>
+          <t>209702</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>94549</t>
+          <t>94362</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130528</t>
+          <t>129634</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>81344</t>
+          <t>79212</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>114155</t>
+          <t>113614</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>182973</t>
+          <t>185320</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>233621</t>
+          <t>236529</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>130460</t>
+          <t>130973</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>177202</t>
+          <t>180669</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>93070</t>
+          <t>90551</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>131500</t>
+          <t>130865</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>233025</t>
+          <t>233925</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>299007</t>
+          <t>294801</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>162868</t>
+          <t>164250</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>216988</t>
+          <t>215049</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129095</t>
+          <t>128212</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>176792</t>
+          <t>174676</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>303796</t>
+          <t>306785</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>373233</t>
+          <t>377115</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>342700</t>
+          <t>341734</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>411205</t>
+          <t>409792</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>238857</t>
+          <t>236716</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>294122</t>
+          <t>294006</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>596678</t>
+          <t>598207</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>686570</t>
+          <t>686104</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>290987</t>
+          <t>289668</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>353453</t>
+          <t>351943</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>210796</t>
+          <t>210784</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>266907</t>
+          <t>264674</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>518572</t>
+          <t>514668</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>603207</t>
+          <t>596124</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>348712</t>
+          <t>350620</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>421042</t>
+          <t>417421</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,49 +7568,49 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>29,35%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>276004</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>249378</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>307040</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>26,61%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>24,04%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
           <t>29,6%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>276004</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>247956</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>304775</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>26,61%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>23,91%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>29,39%</t>
-        </is>
-      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>616</t>
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>613060</t>
+          <t>613053</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>704282</t>
+          <t>708184</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
